--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_los rios.xlsx
@@ -45,12 +45,12 @@
     <t xml:space="preserve">Paillaco</t>
   </si>
   <si>
+    <t xml:space="preserve">Panguipulli</t>
+  </si>
+  <si>
     <t xml:space="preserve">Los Lagos</t>
   </si>
   <si>
-    <t xml:space="preserve">Panguipulli</t>
-  </si>
-  <si>
     <t xml:space="preserve">Río Bueno</t>
   </si>
   <si>
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:35</t>
+    <t xml:space="preserve">2026-09-09 23:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -562,7 +562,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>14104</v>
+        <v>14108</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
@@ -579,7 +579,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>14108</v>
+        <v>14104</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:34</t>
+    <t xml:space="preserve">2026-09-17 14:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_los rios.xlsx
@@ -45,12 +45,12 @@
     <t xml:space="preserve">Paillaco</t>
   </si>
   <si>
+    <t xml:space="preserve">Los Lagos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Panguipulli</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Lagos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Río Bueno</t>
   </si>
   <si>
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:28</t>
+    <t xml:space="preserve">2026-09-23 12:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -562,7 +562,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>14108</v>
+        <v>14104</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
@@ -579,7 +579,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>14104</v>
+        <v>14108</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_los rios.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:56</t>
+    <t xml:space="preserve">2026-10-01 23:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre salario mínimo (%)</t>
+    <t xml:space="preserve">% con ingreso igual al mínimo</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -112,9 +112,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre salario mínimo</t>
   </si>
 </sst>
 </file>
@@ -784,7 +781,7 @@
         <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:23</t>
+    <t xml:space="preserve">2026-10-02 11:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:28</t>
+    <t xml:space="preserve">2026-10-02 15:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:23</t>
+    <t xml:space="preserve">2026-10-05 12:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
